--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T20:04:21+00:00</t>
+    <t>2026-05-05T20:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T20:06:51+00:00</t>
+    <t>2026-05-05T20:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T20:17:53+00:00</t>
+    <t>2026-05-06T07:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:26:41+00:00</t>
+    <t>2026-05-06T15:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T15:07:20+00:00</t>
+    <t>2026-05-06T16:39:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T16:39:55+00:00</t>
+    <t>2026-05-06T16:43:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T16:43:09+00:00</t>
+    <t>2026-05-06T16:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
+++ b/release/v2026.3.0/StructureDefinition-mii-ex-pro-questionnaire-capabilities.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T16:46:31+00:00</t>
+    <t>2026-05-08T15:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
